--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,6 +910,30 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>600378</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>昊华科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>601118</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,30 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>600085</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>同仁堂</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>000423</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>东阿阿胶</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
